--- a/sources/anna_step2.xlsx
+++ b/sources/anna_step2.xlsx
@@ -1436,17 +1436,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>d/f+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1461,37 +1461,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>+1 -5</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
+        <is>
+          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
@@ -1500,140 +1485,140 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BT (1_2),2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>– 1,4,2 [~U_~D]</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>+1 0 +2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>+1 0 +2</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
+          <t>–– u/f+3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
+          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1645,88 +1630,103 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>–– u/f+3</t>
+          <t>– 1,(b_d/b_d)+4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>–– 4</t>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>+1 -10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>– 1,(b_d/b_d)+4</t>
+          <t>d/f+1,2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>+1 +1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT (1_2),2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>-8 -5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
+          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
     </row>
@@ -3604,13 +3604,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -4969,7 +4969,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>d/f+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4979,42 +4979,57 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Double Punch</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Does not work starting with d/f+1,2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
@@ -5023,86 +5038,86 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BT (1_2),2</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Double Punch</t>
+          <t>– Bermuda Triangle</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>– 1,4,2 [~U_~D]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>– Snake [SS]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6,15,12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Does not work starting with d/f+1,2</t>
+          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>– Bermuda Triangle</t>
+          <t>–– High Kick</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5110,83 +5125,83 @@
           <t>h</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>–– u/f+3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>–– Bone Cutter</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6,15,12</t>
+          <t>13,10,10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>hhh</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
+          <t>h</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>–– High Kick</t>
+          <t>–– Spin Trip</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
+          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5198,138 +5213,123 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>–– u/f+3</t>
+          <t>– 1,(b_d/b_d)+4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>–– Bone Cutter</t>
+          <t>– Jab Rush - Low Kick</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13,10,10</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>hl</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>–– 4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>–– Spin Trip</t>
+          <t>PDK Combo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
+          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>– 1,(b_d/b_d)+4</t>
+          <t>d/f+1,2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>– Jab Rush - Low Kick</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT (1_2),2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PDK Combo</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
+          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
         </is>
       </c>
     </row>
@@ -7485,50 +7485,6 @@
       <c r="J134" t="inlineStr">
         <is>
           <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>d/f+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>3868d410-2e89-48d9-953a-b6d47bab49c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>(BT 1_2),2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>2f43bade-2f95-4531-9ea3-4cdbb2bdd0bd</t>
         </is>
       </c>
     </row>
